--- a/Events/comparisons/checklist/User_story.xlsx
+++ b/Events/comparisons/checklist/User_story.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\compm\PycharmProjects\Analytics Events\comparisons\checklist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{337C32B9-FBF5-4F9B-8E87-C799027D2642}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39843E9-5B54-4200-86B1-15E281B88773}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19965" windowHeight="7230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="596">
   <si>
     <t>ABTestingResolveCompleted</t>
   </si>
@@ -2223,15 +2223,12 @@
   <si>
     <t>PreciseTime, eventType | Начисление, currencyName | Gold, value, fromWhere | Poker, itemId | NewContent_Rooms, balance | 24900, before</t>
   </si>
-  <si>
-    <t>START</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2290,15 +2287,8 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2329,6 +2319,12 @@
         <bgColor rgb="FFFF9900"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC4125"/>
+        <bgColor rgb="FFCC4125"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2342,7 +2338,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2405,6 +2401,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2426,8 +2423,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4204,13 +4199,13 @@
       <c r="E2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="45" t="s">
+      <c r="F2" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
@@ -4240,11 +4235,11 @@
         <v>1</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
@@ -4274,11 +4269,11 @@
         <v>102</v>
       </c>
       <c r="E4" s="3"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
@@ -4308,11 +4303,11 @@
         <v>540</v>
       </c>
       <c r="E5" s="3"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
@@ -4342,11 +4337,11 @@
         <v>104</v>
       </c>
       <c r="E6" s="3"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
@@ -4374,11 +4369,11 @@
       <c r="E7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="43"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
@@ -4404,11 +4399,11 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="43"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
@@ -4440,13 +4435,13 @@
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="43" t="s">
+      <c r="F9" s="42" t="s">
         <v>107</v>
       </c>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="44"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
@@ -4472,13 +4467,13 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="43" t="s">
+      <c r="F10" s="42" t="s">
         <v>108</v>
       </c>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="44"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -4504,13 +4499,13 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="43" t="s">
+      <c r="F11" s="42" t="s">
         <v>109</v>
       </c>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="44"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -4544,13 +4539,13 @@
         <v>111</v>
       </c>
       <c r="E12" s="3"/>
-      <c r="F12" s="43" t="s">
+      <c r="F12" s="42" t="s">
         <v>541</v>
       </c>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -4580,13 +4575,13 @@
         <v>112</v>
       </c>
       <c r="E13" s="3"/>
-      <c r="F13" s="43" t="s">
+      <c r="F13" s="42" t="s">
         <v>113</v>
       </c>
-      <c r="G13" s="44"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="44"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
@@ -4612,13 +4607,13 @@
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
-      <c r="F14" s="43" t="s">
+      <c r="F14" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="44"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -4644,13 +4639,13 @@
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="43" t="s">
+      <c r="F15" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="G15" s="44"/>
-      <c r="H15" s="44"/>
-      <c r="I15" s="44"/>
-      <c r="J15" s="44"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
@@ -4684,13 +4679,13 @@
         <v>1</v>
       </c>
       <c r="E16" s="3"/>
-      <c r="F16" s="43" t="s">
+      <c r="F16" s="42" t="s">
         <v>117</v>
       </c>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="44"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -4716,13 +4711,13 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
-      <c r="F17" s="43" t="s">
+      <c r="F17" s="42" t="s">
         <v>118</v>
       </c>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="44"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
@@ -4748,13 +4743,13 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
-      <c r="F18" s="46" t="s">
+      <c r="F18" s="45" t="s">
         <v>542</v>
       </c>
-      <c r="G18" s="44"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="44"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
@@ -4780,13 +4775,13 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
-      <c r="F19" s="46" t="s">
+      <c r="F19" s="45" t="s">
         <v>543</v>
       </c>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
@@ -4876,11 +4871,11 @@
         <v>121</v>
       </c>
       <c r="E22" s="3"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="44"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
@@ -6277,6 +6272,7 @@
       <c r="AB63" s="3"/>
     </row>
     <row r="64" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A64" s="3"/>
       <c r="B64" s="13"/>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
@@ -6402,7 +6398,7 @@
       <c r="AB67" s="3"/>
     </row>
     <row r="68" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A68" s="41"/>
+      <c r="A68" s="32"/>
       <c r="D68" s="7"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
@@ -6430,9 +6426,7 @@
       <c r="AB68" s="3"/>
     </row>
     <row r="69" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A69" s="42" t="s">
-        <v>596</v>
-      </c>
+      <c r="A69" s="8"/>
       <c r="B69" s="13"/>
       <c r="C69" s="3"/>
       <c r="D69" s="7"/>
@@ -6530,7 +6524,7 @@
       <c r="AB71" s="3"/>
     </row>
     <row r="72" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B72" s="32"/>
+      <c r="B72" s="33"/>
       <c r="C72" s="1" t="s">
         <v>549</v>
       </c>
@@ -7155,7 +7149,7 @@
       <c r="AB90" s="3"/>
     </row>
     <row r="91" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B91" s="32"/>
+      <c r="B91" s="33"/>
       <c r="C91" s="3" t="s">
         <v>52</v>
       </c>
@@ -7319,7 +7313,7 @@
       <c r="AB95" s="3"/>
     </row>
     <row r="96" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B96" s="32"/>
+      <c r="B96" s="33"/>
       <c r="C96" s="3" t="s">
         <v>13</v>
       </c>
@@ -7352,7 +7346,7 @@
       <c r="AB96" s="3"/>
     </row>
     <row r="97" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B97" s="32"/>
+      <c r="B97" s="33"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
       <c r="G97" s="3"/>
@@ -7379,7 +7373,7 @@
       <c r="AB97" s="3"/>
     </row>
     <row r="98" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B98" s="32"/>
+      <c r="B98" s="33"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
       <c r="G98" s="3"/>
@@ -7665,7 +7659,7 @@
       <c r="C107" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D107" s="40" t="s">
+      <c r="D107" s="41" t="s">
         <v>593</v>
       </c>
       <c r="E107" s="3"/>
@@ -7720,9 +7714,6 @@
       <c r="AB108" s="3"/>
     </row>
     <row r="109" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A109" s="41" t="s">
-        <v>575</v>
-      </c>
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
       <c r="G109" s="3"/>
@@ -7775,8 +7766,8 @@
       <c r="AB110" s="3"/>
     </row>
     <row r="111" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A111" s="8">
-        <v>21</v>
+      <c r="A111" s="8" t="s">
+        <v>575</v>
       </c>
       <c r="B111" s="12" t="s">
         <v>569</v>
@@ -7954,7 +7945,7 @@
       <c r="C116" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D116" s="40" t="s">
+      <c r="D116" s="41" t="s">
         <v>594</v>
       </c>
       <c r="E116" s="3"/>
@@ -8351,7 +8342,7 @@
       <c r="C128" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D128" s="40" t="s">
+      <c r="D128" s="41" t="s">
         <v>595</v>
       </c>
       <c r="E128" s="3"/>
@@ -9408,7 +9399,7 @@
       <c r="AB163" s="3"/>
     </row>
     <row r="164" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A164" s="33" t="s">
+      <c r="A164" s="34" t="s">
         <v>575</v>
       </c>
       <c r="B164" s="13"/>
@@ -9443,10 +9434,10 @@
       <c r="A165" s="8">
         <v>20</v>
       </c>
-      <c r="B165" s="34" t="s">
+      <c r="B165" s="35" t="s">
         <v>576</v>
       </c>
-      <c r="C165" s="35" t="s">
+      <c r="C165" s="36" t="s">
         <v>577</v>
       </c>
       <c r="D165" s="5"/>
@@ -10618,7 +10609,7 @@
       <c r="AB200" s="3"/>
     </row>
     <row r="201" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B201" s="32"/>
+      <c r="B201" s="33"/>
       <c r="C201" s="3" t="s">
         <v>92</v>
       </c>
@@ -24560,7 +24551,7 @@
     </row>
     <row r="624" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A624" s="14"/>
-      <c r="B624" s="36"/>
+      <c r="B624" s="37"/>
       <c r="C624" s="15"/>
       <c r="D624" s="16"/>
       <c r="E624" s="3"/>
@@ -24590,7 +24581,7 @@
     </row>
     <row r="625" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A625" s="14"/>
-      <c r="B625" s="36"/>
+      <c r="B625" s="37"/>
       <c r="C625" s="15"/>
       <c r="D625" s="16"/>
       <c r="E625" s="3"/>
@@ -24622,7 +24613,7 @@
       <c r="A626" s="14">
         <v>125</v>
       </c>
-      <c r="B626" s="37" t="s">
+      <c r="B626" s="38" t="s">
         <v>377</v>
       </c>
       <c r="C626" s="15" t="s">
@@ -24658,7 +24649,7 @@
     </row>
     <row r="627" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A627" s="15"/>
-      <c r="B627" s="36"/>
+      <c r="B627" s="37"/>
       <c r="C627" s="15" t="s">
         <v>92</v>
       </c>
@@ -24692,7 +24683,7 @@
     </row>
     <row r="628" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A628" s="15"/>
-      <c r="B628" s="36"/>
+      <c r="B628" s="37"/>
       <c r="C628" s="15" t="s">
         <v>92</v>
       </c>
@@ -24726,7 +24717,7 @@
     </row>
     <row r="629" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A629" s="15"/>
-      <c r="B629" s="36"/>
+      <c r="B629" s="37"/>
       <c r="C629" s="15" t="s">
         <v>92</v>
       </c>
@@ -24760,7 +24751,7 @@
     </row>
     <row r="630" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A630" s="15"/>
-      <c r="B630" s="36"/>
+      <c r="B630" s="37"/>
       <c r="C630" s="15" t="s">
         <v>67</v>
       </c>
@@ -24794,7 +24785,7 @@
     </row>
     <row r="631" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A631" s="15"/>
-      <c r="B631" s="36"/>
+      <c r="B631" s="37"/>
       <c r="C631" s="15"/>
       <c r="D631" s="15"/>
       <c r="E631" s="3"/>
@@ -24824,7 +24815,7 @@
     </row>
     <row r="632" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A632" s="15"/>
-      <c r="B632" s="36"/>
+      <c r="B632" s="37"/>
       <c r="C632" s="15"/>
       <c r="D632" s="15"/>
       <c r="E632" s="3"/>
@@ -24856,7 +24847,7 @@
       <c r="A633" s="11">
         <v>126</v>
       </c>
-      <c r="B633" s="37" t="s">
+      <c r="B633" s="38" t="s">
         <v>292</v>
       </c>
       <c r="C633" s="15" t="s">
@@ -24892,7 +24883,7 @@
     </row>
     <row r="634" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A634" s="15"/>
-      <c r="B634" s="36"/>
+      <c r="B634" s="37"/>
       <c r="C634" s="15"/>
       <c r="D634" s="15"/>
       <c r="E634" s="3"/>
@@ -24922,7 +24913,7 @@
     </row>
     <row r="635" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A635" s="15"/>
-      <c r="B635" s="36"/>
+      <c r="B635" s="37"/>
       <c r="C635" s="15"/>
       <c r="D635" s="15"/>
       <c r="E635" s="3"/>
@@ -24954,7 +24945,7 @@
       <c r="A636" s="14">
         <v>127</v>
       </c>
-      <c r="B636" s="36" t="s">
+      <c r="B636" s="37" t="s">
         <v>379</v>
       </c>
       <c r="C636" s="15" t="s">
@@ -24990,7 +24981,7 @@
     </row>
     <row r="637" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A637" s="15"/>
-      <c r="B637" s="36"/>
+      <c r="B637" s="37"/>
       <c r="C637" s="15" t="s">
         <v>92</v>
       </c>
@@ -25024,7 +25015,7 @@
     </row>
     <row r="638" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A638" s="15"/>
-      <c r="B638" s="36"/>
+      <c r="B638" s="37"/>
       <c r="C638" s="15" t="s">
         <v>92</v>
       </c>
@@ -25058,7 +25049,7 @@
     </row>
     <row r="639" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A639" s="15"/>
-      <c r="B639" s="36"/>
+      <c r="B639" s="37"/>
       <c r="C639" s="15" t="s">
         <v>92</v>
       </c>
@@ -25092,7 +25083,7 @@
     </row>
     <row r="640" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A640" s="15"/>
-      <c r="B640" s="36"/>
+      <c r="B640" s="37"/>
       <c r="C640" s="15"/>
       <c r="D640" s="15"/>
       <c r="E640" s="3"/>
@@ -25122,7 +25113,7 @@
     </row>
     <row r="641" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A641" s="15"/>
-      <c r="B641" s="36"/>
+      <c r="B641" s="37"/>
       <c r="C641" s="15"/>
       <c r="D641" s="15"/>
       <c r="E641" s="3"/>
@@ -25154,7 +25145,7 @@
       <c r="A642" s="14">
         <v>128</v>
       </c>
-      <c r="B642" s="36" t="s">
+      <c r="B642" s="37" t="s">
         <v>380</v>
       </c>
       <c r="C642" s="15" t="s">
@@ -25190,7 +25181,7 @@
     </row>
     <row r="643" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A643" s="15"/>
-      <c r="B643" s="36"/>
+      <c r="B643" s="37"/>
       <c r="C643" s="15" t="s">
         <v>13</v>
       </c>
@@ -25224,7 +25215,7 @@
     </row>
     <row r="644" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A644" s="15"/>
-      <c r="B644" s="36"/>
+      <c r="B644" s="37"/>
       <c r="C644" s="15" t="s">
         <v>13</v>
       </c>
@@ -25258,7 +25249,7 @@
     </row>
     <row r="645" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A645" s="15"/>
-      <c r="B645" s="36"/>
+      <c r="B645" s="37"/>
       <c r="C645" s="15" t="s">
         <v>13</v>
       </c>
@@ -25292,7 +25283,7 @@
     </row>
     <row r="646" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A646" s="15"/>
-      <c r="B646" s="36"/>
+      <c r="B646" s="37"/>
       <c r="C646" s="15" t="s">
         <v>92</v>
       </c>
@@ -25326,7 +25317,7 @@
     </row>
     <row r="647" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A647" s="15"/>
-      <c r="B647" s="36"/>
+      <c r="B647" s="37"/>
       <c r="C647" s="15"/>
       <c r="D647" s="15"/>
       <c r="E647" s="3"/>
@@ -25356,7 +25347,7 @@
     </row>
     <row r="648" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A648" s="15"/>
-      <c r="B648" s="36"/>
+      <c r="B648" s="37"/>
       <c r="C648" s="15"/>
       <c r="D648" s="15"/>
       <c r="E648" s="3"/>
@@ -25388,7 +25379,7 @@
       <c r="A649" s="14">
         <v>129</v>
       </c>
-      <c r="B649" s="36" t="s">
+      <c r="B649" s="37" t="s">
         <v>384</v>
       </c>
       <c r="C649" s="15" t="s">
@@ -25424,7 +25415,7 @@
     </row>
     <row r="650" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A650" s="15"/>
-      <c r="B650" s="36"/>
+      <c r="B650" s="37"/>
       <c r="C650" s="16" t="s">
         <v>8</v>
       </c>
@@ -25458,7 +25449,7 @@
     </row>
     <row r="651" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A651" s="15"/>
-      <c r="B651" s="36"/>
+      <c r="B651" s="37"/>
       <c r="C651" s="16" t="s">
         <v>8</v>
       </c>
@@ -25492,7 +25483,7 @@
     </row>
     <row r="652" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A652" s="15"/>
-      <c r="B652" s="36"/>
+      <c r="B652" s="37"/>
       <c r="C652" s="16" t="s">
         <v>8</v>
       </c>
@@ -25526,7 +25517,7 @@
     </row>
     <row r="653" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A653" s="15"/>
-      <c r="B653" s="36"/>
+      <c r="B653" s="37"/>
       <c r="C653" s="15"/>
       <c r="D653" s="15"/>
       <c r="E653" s="3"/>
@@ -25556,7 +25547,7 @@
     </row>
     <row r="654" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A654" s="15"/>
-      <c r="B654" s="36"/>
+      <c r="B654" s="37"/>
       <c r="C654" s="15"/>
       <c r="D654" s="15"/>
       <c r="E654" s="3"/>
@@ -25588,7 +25579,7 @@
       <c r="A655" s="14">
         <v>130</v>
       </c>
-      <c r="B655" s="36" t="s">
+      <c r="B655" s="37" t="s">
         <v>313</v>
       </c>
       <c r="C655" s="15" t="s">
@@ -25624,7 +25615,7 @@
     </row>
     <row r="656" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A656" s="15"/>
-      <c r="B656" s="36"/>
+      <c r="B656" s="37"/>
       <c r="C656" s="15" t="s">
         <v>92</v>
       </c>
@@ -25658,7 +25649,7 @@
     </row>
     <row r="657" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A657" s="15"/>
-      <c r="B657" s="36"/>
+      <c r="B657" s="37"/>
       <c r="C657" s="15" t="s">
         <v>92</v>
       </c>
@@ -25692,7 +25683,7 @@
     </row>
     <row r="658" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A658" s="15"/>
-      <c r="B658" s="36"/>
+      <c r="B658" s="37"/>
       <c r="C658" s="15" t="s">
         <v>92</v>
       </c>
@@ -25726,7 +25717,7 @@
     </row>
     <row r="659" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A659" s="18"/>
-      <c r="B659" s="38"/>
+      <c r="B659" s="39"/>
       <c r="C659" s="15" t="s">
         <v>74</v>
       </c>
@@ -25760,7 +25751,7 @@
     </row>
     <row r="660" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A660" s="18"/>
-      <c r="B660" s="38"/>
+      <c r="B660" s="39"/>
       <c r="C660" s="15" t="s">
         <v>75</v>
       </c>
@@ -25794,7 +25785,7 @@
     </row>
     <row r="661" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A661" s="18"/>
-      <c r="B661" s="38"/>
+      <c r="B661" s="39"/>
       <c r="C661" s="18"/>
       <c r="D661" s="18"/>
       <c r="E661" s="3"/>
@@ -25824,7 +25815,7 @@
     </row>
     <row r="662" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A662" s="18"/>
-      <c r="B662" s="38"/>
+      <c r="B662" s="39"/>
       <c r="C662" s="18"/>
       <c r="D662" s="18"/>
       <c r="E662" s="3"/>
@@ -25856,7 +25847,7 @@
       <c r="A663" s="14">
         <v>131</v>
       </c>
-      <c r="B663" s="36" t="s">
+      <c r="B663" s="37" t="s">
         <v>389</v>
       </c>
       <c r="C663" s="15" t="s">
@@ -25892,7 +25883,7 @@
     </row>
     <row r="664" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A664" s="15"/>
-      <c r="B664" s="36"/>
+      <c r="B664" s="37"/>
       <c r="C664" s="15" t="s">
         <v>78</v>
       </c>
@@ -25926,7 +25917,7 @@
     </row>
     <row r="665" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A665" s="15"/>
-      <c r="B665" s="36"/>
+      <c r="B665" s="37"/>
       <c r="C665" s="15"/>
       <c r="D665" s="15"/>
       <c r="E665" s="3"/>
@@ -25956,7 +25947,7 @@
     </row>
     <row r="666" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A666" s="15"/>
-      <c r="B666" s="36"/>
+      <c r="B666" s="37"/>
       <c r="C666" s="15"/>
       <c r="D666" s="15"/>
       <c r="E666" s="3"/>
@@ -25988,7 +25979,7 @@
       <c r="A667" s="14">
         <v>132</v>
       </c>
-      <c r="B667" s="36" t="s">
+      <c r="B667" s="37" t="s">
         <v>391</v>
       </c>
       <c r="C667" s="15" t="s">
@@ -26022,7 +26013,7 @@
     </row>
     <row r="668" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A668" s="15"/>
-      <c r="B668" s="36"/>
+      <c r="B668" s="37"/>
       <c r="C668" s="15"/>
       <c r="D668" s="15"/>
       <c r="E668" s="3"/>
@@ -26052,7 +26043,7 @@
     </row>
     <row r="669" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A669" s="15"/>
-      <c r="B669" s="36"/>
+      <c r="B669" s="37"/>
       <c r="C669" s="15"/>
       <c r="D669" s="15"/>
       <c r="E669" s="3"/>
@@ -26084,7 +26075,7 @@
       <c r="A670" s="14">
         <v>133</v>
       </c>
-      <c r="B670" s="36" t="s">
+      <c r="B670" s="37" t="s">
         <v>392</v>
       </c>
       <c r="C670" s="15" t="s">
@@ -26120,7 +26111,7 @@
     </row>
     <row r="671" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A671" s="15"/>
-      <c r="B671" s="36"/>
+      <c r="B671" s="37"/>
       <c r="C671" s="15" t="s">
         <v>92</v>
       </c>
@@ -26154,7 +26145,7 @@
     </row>
     <row r="672" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A672" s="15"/>
-      <c r="B672" s="36"/>
+      <c r="B672" s="37"/>
       <c r="C672" s="15"/>
       <c r="D672" s="15"/>
       <c r="E672" s="3"/>
@@ -26186,7 +26177,7 @@
       <c r="A673" s="14">
         <v>134</v>
       </c>
-      <c r="B673" s="36" t="s">
+      <c r="B673" s="37" t="s">
         <v>393</v>
       </c>
       <c r="C673" s="15" t="s">
@@ -26222,7 +26213,7 @@
     </row>
     <row r="674" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A674" s="15"/>
-      <c r="B674" s="36"/>
+      <c r="B674" s="37"/>
       <c r="C674" s="15"/>
       <c r="D674" s="16" t="s">
         <v>394</v>
@@ -26254,7 +26245,7 @@
     </row>
     <row r="675" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A675" s="15"/>
-      <c r="B675" s="36"/>
+      <c r="B675" s="37"/>
       <c r="C675" s="15"/>
       <c r="D675" s="15"/>
       <c r="E675" s="3"/>
@@ -26284,7 +26275,7 @@
     </row>
     <row r="676" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A676" s="15"/>
-      <c r="B676" s="36"/>
+      <c r="B676" s="37"/>
       <c r="C676" s="15"/>
       <c r="D676" s="15"/>
       <c r="E676" s="3"/>
@@ -26316,7 +26307,7 @@
       <c r="A677" s="14">
         <v>135</v>
       </c>
-      <c r="B677" s="36" t="s">
+      <c r="B677" s="37" t="s">
         <v>368</v>
       </c>
       <c r="C677" s="15" t="s">
@@ -26352,7 +26343,7 @@
     </row>
     <row r="678" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A678" s="15"/>
-      <c r="B678" s="36"/>
+      <c r="B678" s="37"/>
       <c r="C678" s="15"/>
       <c r="D678" s="15"/>
       <c r="E678" s="3"/>
@@ -26382,7 +26373,7 @@
     </row>
     <row r="679" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A679" s="15"/>
-      <c r="B679" s="36"/>
+      <c r="B679" s="37"/>
       <c r="C679" s="15"/>
       <c r="D679" s="15"/>
       <c r="E679" s="3"/>
@@ -26414,7 +26405,7 @@
       <c r="A680" s="14">
         <v>136</v>
       </c>
-      <c r="B680" s="36" t="s">
+      <c r="B680" s="37" t="s">
         <v>395</v>
       </c>
       <c r="C680" s="15" t="s">
@@ -26450,7 +26441,7 @@
     </row>
     <row r="681" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A681" s="19"/>
-      <c r="B681" s="39"/>
+      <c r="B681" s="40"/>
       <c r="C681" s="19"/>
       <c r="D681" s="19"/>
       <c r="E681" s="3"/>
@@ -26479,7 +26470,7 @@
       <c r="AB681" s="3"/>
     </row>
     <row r="682" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B682" s="32"/>
+      <c r="B682" s="33"/>
       <c r="E682" s="3"/>
       <c r="F682" s="3"/>
       <c r="G682" s="3"/>
